--- a/data/accounts_data.xlsx
+++ b/data/accounts_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realaskaer/PycharmProjects/MovementMachine/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realaskaer/PycharmProjects/AstrumMachineDev/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF907F6-2DFB-B340-B416-839FA9CE882C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54266205-E3BD-C344-B3B7-22FC279927F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>Name</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>user@mail.ru:pass</t>
+  </si>
+  <si>
+    <t>Aptos Private Key</t>
+  </si>
+  <si>
+    <t>Sui Private Key</t>
   </si>
 </sst>
 </file>
@@ -474,12 +480,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1751AD-08BF-8141-A6B2-846BFCE83C68}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.5" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" customWidth="1"/>
     <col min="5" max="5" width="20.5" customWidth="1"/>
     <col min="6" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
@@ -488,7 +494,7 @@
     <col min="11" max="11" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -496,34 +502,40 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -531,19 +543,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>6</v>
@@ -557,8 +569,14 @@
       <c r="K2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -570,8 +588,10 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -583,8 +603,10 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
-    </row>
-    <row r="5" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+    </row>
+    <row r="5" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -596,8 +618,10 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+    </row>
+    <row r="6" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -609,8 +633,10 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+    </row>
+    <row r="7" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -622,8 +648,10 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
-    </row>
-    <row r="8" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -635,8 +663,10 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
-    </row>
-    <row r="9" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -648,8 +678,10 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -661,8 +693,10 @@
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -674,8 +708,10 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+    </row>
+    <row r="12" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -687,8 +723,10 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+    </row>
+    <row r="13" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -700,8 +738,10 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
-    </row>
-    <row r="14" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+    </row>
+    <row r="14" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -713,8 +753,10 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
-    </row>
-    <row r="15" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+    </row>
+    <row r="15" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -726,8 +768,10 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
-    </row>
-    <row r="16" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -739,8 +783,10 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
-    </row>
-    <row r="17" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+    </row>
+    <row r="17" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -752,8 +798,10 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+    </row>
+    <row r="18" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -765,8 +813,10 @@
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="1:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+    </row>
+    <row r="19" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -778,8 +828,10 @@
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="1:11" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+    </row>
+    <row r="20" spans="1:13" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/accounts_data.xlsx
+++ b/data/accounts_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realaskaer/PycharmProjects/AstrumMachineDev/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realaskaer/PycharmProjects/AstrumMachine/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54266205-E3BD-C344-B3B7-22FC279927F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E01024E-4270-A44B-A84D-9313C408DABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -56,9 +56,6 @@
     <t>EVM Private Key</t>
   </si>
   <si>
-    <t>123token</t>
-  </si>
-  <si>
     <t>Twitter ct0</t>
   </si>
   <si>
@@ -77,26 +74,32 @@
     <t>Reserve Twitter Token</t>
   </si>
   <si>
+    <t>0x123</t>
+  </si>
+  <si>
+    <t>Aptos Private Key</t>
+  </si>
+  <si>
+    <t>Sui Private Key</t>
+  </si>
+  <si>
+    <t>CEX Address</t>
+  </si>
+  <si>
     <t>log:pass@ip:port</t>
   </si>
   <si>
-    <t>0x123</t>
-  </si>
-  <si>
-    <t>user@mail.ru:pass</t>
-  </si>
-  <si>
-    <t>Aptos Private Key</t>
-  </si>
-  <si>
-    <t>Sui Private Key</t>
+    <t>login:pass</t>
+  </si>
+  <si>
+    <t>abc123</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -137,8 +140,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6AAB73"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFBCBEC4"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +178,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +215,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -194,6 +224,9 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Контрольная ячейка" xfId="1" builtinId="23"/>
@@ -480,8 +513,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1751AD-08BF-8141-A6B2-846BFCE83C68}">
-  <dimension ref="A1:M20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24.5" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
@@ -490,11 +523,14 @@
     <col min="6" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="40" customWidth="1"/>
     <col min="9" max="9" width="32.5" customWidth="1"/>
-    <col min="10" max="10" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="27.6640625" customWidth="1"/>
     <col min="11" max="11" width="24.5" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="27.6640625" customWidth="1"/>
+    <col min="14" max="14" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" ht="21" thickTop="1" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -502,336 +538,94 @@
         <v>5</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="17" thickTop="1" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+    <row r="3" spans="1:14" ht="16" thickTop="1">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="5" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-    </row>
-    <row r="7" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-    </row>
-    <row r="17" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-    </row>
-    <row r="18" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-    </row>
-    <row r="19" spans="1:13" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-    </row>
-    <row r="20" spans="1:13" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/accounts_data.xlsx
+++ b/data/accounts_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/realaskaer/PycharmProjects/AstrumMachine/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80084E25-564A-514D-B6FB-0ADE8C416937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0372669A-2112-C14B-9BC7-F2C530CB56B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Name</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>login:password:2fa:token:ct0</t>
+  </si>
+  <si>
+    <t>Bitcoin</t>
   </si>
 </sst>
 </file>
@@ -514,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E1751AD-08BF-8141-A6B2-846BFCE83C68}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24.5" customWidth="1"/>
@@ -540,7 +543,7 @@
     <col min="23" max="23" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="21" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,37 +557,40 @@
         <v>12</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -597,38 +603,41 @@
       <c r="D2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -643,8 +652,9 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
-    </row>
-    <row r="4" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -659,8 +669,9 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-    </row>
-    <row r="5" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O4" s="1"/>
+    </row>
+    <row r="5" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -675,8 +686,9 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
-    </row>
-    <row r="6" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -691,8 +703,9 @@
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
-    </row>
-    <row r="7" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O6" s="1"/>
+    </row>
+    <row r="7" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -707,8 +720,9 @@
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
-    </row>
-    <row r="8" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O7" s="1"/>
+    </row>
+    <row r="8" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -723,8 +737,9 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-    </row>
-    <row r="9" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="1"/>
+    </row>
+    <row r="9" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -739,8 +754,9 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O9" s="1"/>
+    </row>
+    <row r="10" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -755,8 +771,9 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-    </row>
-    <row r="11" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O10" s="1"/>
+    </row>
+    <row r="11" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -771,8 +788,9 @@
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
-    </row>
-    <row r="12" spans="1:14" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="O11" s="1"/>
+    </row>
+    <row r="12" spans="1:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -787,8 +805,9 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="O12" s="1"/>
+    </row>
+    <row r="13" spans="1:15" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
